--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1,37 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="الموظفين" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="الغيابات" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="البدلات" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="الحضور" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,21 +51,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -79,44 +139,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -143,15 +203,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -178,7 +237,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -190,150 +248,440 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>الموظف</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>القسم</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الوظيفة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الرقم الكودي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>خط السير</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الوردية</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>تاريخ التوظيف</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>رقم الهاتف</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>الرصيد السنوي</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>محمد</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>الموظف</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>القسم</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>نوع الغياب</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>عدد الأيام</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>سبب الغياب</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>موثق</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>الموظف</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>القسم</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>نوع البدل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>المبلغ</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>الموظف</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>القسم</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>وقت الحضور</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>وقت الانصراف</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>عدد ساعات العمل</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="الموظفين" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="الغيابات" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="البدلات" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="الحضور" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="الغيابات" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="البدلات" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="الحضور" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="قطع_الغيار" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="صيانة_وقائية" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,72 +447,39 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>الوظيفة</t>
+          <t>التاريخ</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>الرقم الكودي</t>
+          <t>نوع الغياب</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>خط السير</t>
+          <t>عدد الأيام</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>الوردية</t>
+          <t>سبب الغياب</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>تاريخ التوظيف</t>
+          <t>موثق</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>رقم الهاتف</t>
+          <t>ملاحظات</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>الرصيد السنوي</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
           <t>رابط الصورة</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>محمد</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -519,67 +487,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>الموظف</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>القسم</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>نوع الغياب</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>عدد الأيام</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>سبب الغياب</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>موثق</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>رابط الصورة</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -620,6 +527,62 @@
         </is>
       </c>
       <c r="G1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>الموظف</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>القسم</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>وقت الحضور</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>وقت الانصراف</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>عدد ساعات العمل</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>رابط الصورة</t>
         </is>
@@ -642,32 +605,88 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>الموظف</t>
+          <t>اسم القطعة</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>المقاس</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>قوه الشد</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الرصيد الموجود</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>مدة التوريد</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ضرورية</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>القسم</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>رابط_الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>نوع_الصيانة</t>
+        </is>
+      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>التاريخ</t>
+          <t>اسم_البند</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>وقت الحضور</t>
+          <t>الفترة_بالأيام</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>وقت الانصراف</t>
+          <t>آخر_تنفيذ</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>عدد ساعات العمل</t>
+          <t>التاريخ_التالي</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -677,7 +696,12 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>رابط الصورة</t>
+          <t>قطع_غيار_مستخدمة_افتراضية</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>رابط_الصورة</t>
         </is>
       </c>
     </row>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -8,11 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="الغيابات" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="البدلات" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="الحضور" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="قطع_الغيار" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="صيانة_وقائية" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="البدلات" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="الحضور" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="قطع_الغيار" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="صيانة_وقائية" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,30 +451,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>نوع الغياب</t>
+          <t>نوع البدل</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>عدد الأيام</t>
+          <t>المبلغ</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>سبب الغياب</t>
+          <t>ملاحظات</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>موثق</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>رابط الصورة</t>
         </is>
@@ -492,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,20 +502,25 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>نوع البدل</t>
+          <t>وقت الحضور</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>المبلغ</t>
+          <t>وقت الانصراف</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>عدد ساعات العمل</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>ملاحظات</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>رابط الصورة</t>
         </is>
@@ -549,42 +543,42 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>الموظف</t>
+          <t>اسم القطعة</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>المقاس</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>قوه الشد</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الرصيد الموجود</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>مدة التوريد</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ضرورية</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>القسم</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>وقت الحضور</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>وقت الانصراف</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>عدد ساعات العمل</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>رابط الصورة</t>
+          <t>رابط_الصورة</t>
         </is>
       </c>
     </row>
@@ -594,62 +588,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>اسم القطعة</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>المقاس</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>قوه الشد</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الرصيد الموجود</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>مدة التوريد</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>ضرورية</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>القسم</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>رابط_الصورة</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -8,10 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="البدلات" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="الحضور" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="قطع_الغيار" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="صيانة_وقائية" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="الحضور" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="قطع_الغيار" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="صيانة_وقائية" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,20 +450,25 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>نوع البدل</t>
+          <t>وقت الحضور</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>المبلغ</t>
+          <t>وقت الانصراف</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>عدد ساعات العمل</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>ملاحظات</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>رابط الصورة</t>
         </is>
@@ -487,42 +491,42 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>الموظف</t>
+          <t>اسم القطعة</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>المقاس</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>قوه الشد</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الرصيد الموجود</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>مدة التوريد</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ضرورية</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>القسم</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>وقت الحضور</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>وقت الانصراف</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>عدد ساعات العمل</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>رابط الصورة</t>
+          <t>رابط_الصورة</t>
         </is>
       </c>
     </row>
@@ -532,62 +536,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>اسم القطعة</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>المقاس</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>قوه الشد</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الرصيد الموجود</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>مدة التوريد</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>ضرورية</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>القسم</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>رابط_الصورة</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -8,9 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="الحضور" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="قطع_الغيار" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="صيانة_وقائية" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="قطع_الغيار" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="صيانة_وقائية" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,42 +434,42 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>الموظف</t>
+          <t>اسم القطعة</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>المقاس</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>قوه الشد</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الرصيد الموجود</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>مدة التوريد</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ضرورية</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>القسم</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>وقت الحضور</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>وقت الانصراف</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>عدد ساعات العمل</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>رابط الصورة</t>
+          <t>رابط_الصورة</t>
         </is>
       </c>
     </row>
@@ -485,62 +484,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>اسم القطعة</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>المقاس</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>قوه الشد</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الرصيد الموجود</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>مدة التوريد</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>ضرورية</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>القسم</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>رابط_الصورة</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="قطع_الغيار" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="صيانة_وقائية" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="الكرد" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -537,4 +538,75 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -7,10 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="قطع_الغيار" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="صيانة_وقائية" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="الكرد" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="قطع_الغيار" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="صيانة_وقائية" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="الكرد" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,9 +415,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>اسم القطعة</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المقاس</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>قوه الشد</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الرصيد الموجود</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>مدة التوريد</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ضرورية</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>القسم</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>رابط_الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -429,46 +471,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>اسم القطعة</t>
+          <t>المعدة</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>المقاس</t>
+          <t>نوع_الصيانة</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>قوه الشد</t>
+          <t>اسم_البند</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>الرصيد الموجود</t>
+          <t>الفترة_بالأيام</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>مدة التوريد</t>
+          <t>آخر_تنفيذ</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>ضرورية</t>
+          <t>التاريخ_التالي</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>القسم</t>
+          <t>ملاحظات</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
+        <is>
+          <t>قطع_غيار_مستخدمة_افتراضية</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>رابط_الصورة</t>
         </is>
@@ -485,67 +532,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>نوع_الصيانة</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>اسم_البند</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الفترة_بالأيام</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>آخر_تنفيذ</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>التاريخ_التالي</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>قطع_غيار_مستخدمة_افتراضية</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>رابط_الصورة</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -10,6 +10,7 @@
     <sheet name="قطع_الغيار" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="صيانة_وقائية" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="الكرد" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="التمشيط" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,4 +596,75 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -592,6 +592,23 @@
           <t>رابط الصورة</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>كرد1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -621,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,6 +680,23 @@
           <t>رابط الصورة</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>تمشيط 1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -19,7 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -472,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,6 +525,33 @@
           <t>رابط_الصورة</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>تمشيط 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>720 ساعة</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>تشجيم(EP2=20جم)</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -19,9 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -52,9 +54,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -476,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,6 +555,33 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>تمشيط 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>720 ساعة</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>تشجيم(EP2=20جم)</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -10,7 +10,6 @@
     <sheet name="قطع_الغيار" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="صيانة_وقائية" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="الكرد" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="التمشيط" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,11 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -54,10 +51,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -576,7 +572,7 @@
         <v>30</v>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="1" t="n">
         <v>46258</v>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -674,92 +670,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>مده الاصلاح</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الحدث/العطل</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>تم بواسطة</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>قطع غيار مستخدمة</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>نوع العطل</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>الالتزام بتعليمات السلامة</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>رابط الصورة</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>تمشيط 1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="قطع_الغيار" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="صيانة_وقائية" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="الكرد" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -582,92 +581,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>مده الاصلاح</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الحدث/العطل</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>تم بواسطة</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>قطع غيار مستخدمة</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>نوع العطل</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>الالتزام بتعليمات السلامة</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>رابط الصورة</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>كرد1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="قطع_الغيار" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="صيانة_وقائية" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Uin Floc" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -581,4 +582,75 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="قطع_الغيار" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="صيانة_وقائية" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Uin Floc" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -582,75 +581,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>مده الاصلاح</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الحدث/العطل</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>تم بواسطة</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>قطع غيار مستخدمة</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>نوع العطل</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>الالتزام بتعليمات السلامة</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>رابط الصورة</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="قطع_الغيار" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="صيانة_وقائية" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Roving" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -581,4 +582,75 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="قطع_الغيار" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="صيانة_وقائية" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Roving" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -582,75 +581,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>مده الاصلاح</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>المعدة</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>الحدث/العطل</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>الإجراء التصحيحي</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>تم بواسطة</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>قطع غيار مستخدمة</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>نوع العطل</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>الالتزام بتعليمات السلامة</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>رابط الصورة</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="قطع_الغيار" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="صيانة_وقائية" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Bloow Room" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -581,4 +582,75 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,6 +649,23 @@
           <t>رابط الصورة</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uin Floc </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,6 +667,23 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uin Floc </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -684,6 +684,23 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uin Floc </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,6 +701,23 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Uin Clean B15</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -718,6 +718,23 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Uin Mix B76</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -735,6 +735,23 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B17</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,6 +752,23 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Uin Store A79</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,6 +769,23 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LOP Tix</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,23 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>A 21</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,6 +803,23 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>A 49</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -10,6 +10,7 @@
     <sheet name="قطع_الغيار" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="صيانة_وقائية" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Bloow Room" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Card" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -823,4 +824,75 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,6 +892,23 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Card_1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,6 +909,23 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Card_2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,6 +926,23 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Card_3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -943,6 +943,23 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Card_4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -960,6 +960,23 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Card_5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -977,6 +977,23 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Card_6</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -994,6 +994,23 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Card_7</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1011,6 +1011,23 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Card_8</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -11,6 +11,7 @@
     <sheet name="صيانة_وقائية" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Bloow Room" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Card" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Breaker" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1031,4 +1032,75 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1040,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1100,6 +1100,23 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SB_ D27 (M_1)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1040,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1117,6 +1117,23 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SB_ D27 (M_2)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Bloow Room" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Card" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Breaker" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Omega Lap" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1137,4 +1138,75 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1146,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1206,6 +1206,23 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Omega Lap </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Card" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Breaker" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Omega Lap" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Comber" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1226,4 +1227,75 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1235,7 +1235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1295,6 +1295,23 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Comber _1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1235,7 +1235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1312,6 +1312,23 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Comber _2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1235,7 +1235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,6 +1329,23 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Comber _3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1235,7 +1235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1346,6 +1346,23 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Comber _4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1235,7 +1235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1363,6 +1363,23 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Comber _5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1235,7 +1235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1380,6 +1380,23 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Comber _6</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Breaker" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Omega Lap" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Comber" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Finsher" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1400,4 +1401,75 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1409,7 +1409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1469,6 +1469,23 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>RSB_D27 (M_1)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1409,7 +1409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1486,6 +1486,23 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RSB_D27 (M_2)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Omega Lap" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Comber" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Finsher" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Roving" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1506,4 +1507,75 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1515,7 +1515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1575,6 +1575,23 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Roving _1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1515,7 +1515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1592,6 +1592,23 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Roving _2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -1515,7 +1515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1609,6 +1609,23 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Roving _3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -24,9 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -57,9 +59,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -481,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,6 +587,33 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Uin Floc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>660 ساعة</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">فحص واختبار شد سير المحرك </t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,12 +608,39 @@
         <v>27.5</v>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>46259</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Uin Floc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>720 ساعة</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صيانه شهريه كامله للجهاز  فحص مضرب التفتيح وجربوكسات حركه الجهاز لا أعلى واسفل وذهاب وعوده </t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
